--- a/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_area.xlsx
+++ b/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_area.xlsx
@@ -101,10 +101,10 @@
         <v>2001</v>
       </c>
       <c r="C2" s="1">
-        <v>0.37887167930603027</v>
+        <v>0.40664386749267578</v>
       </c>
       <c r="D2" s="1">
-        <v>37.887168884277344</v>
+        <v>40.664386749267578</v>
       </c>
     </row>
     <row r="3">
@@ -115,10 +115,10 @@
         <v>2001</v>
       </c>
       <c r="C3" s="1">
-        <v>0.6405068039894104</v>
+        <v>0.71233052015304565</v>
       </c>
       <c r="D3" s="1">
-        <v>64.050682067871094</v>
+        <v>71.233055114746094</v>
       </c>
     </row>
     <row r="4">
@@ -129,10 +129,10 @@
         <v>2003</v>
       </c>
       <c r="C4" s="1">
-        <v>0.34124886989593506</v>
+        <v>0.33703827857971192</v>
       </c>
       <c r="D4" s="1">
-        <v>34.124885559082031</v>
+        <v>33.703826904296875</v>
       </c>
     </row>
     <row r="5">
@@ -143,10 +143,10 @@
         <v>2003</v>
       </c>
       <c r="C5" s="1">
-        <v>0.65731269121170044</v>
+        <v>0.70703375339508057</v>
       </c>
       <c r="D5" s="1">
-        <v>65.731269836425781</v>
+        <v>70.703376770019531</v>
       </c>
     </row>
     <row r="6">
@@ -157,10 +157,10 @@
         <v>2005</v>
       </c>
       <c r="C6" s="1">
-        <v>0.22490382194519043</v>
+        <v>0.23752780258655548</v>
       </c>
       <c r="D6" s="1">
-        <v>22.490383148193359</v>
+        <v>23.752780914306641</v>
       </c>
     </row>
     <row r="7">
@@ -171,10 +171,10 @@
         <v>2005</v>
       </c>
       <c r="C7" s="1">
-        <v>0.52277326583862305</v>
+        <v>0.58777987957000732</v>
       </c>
       <c r="D7" s="1">
-        <v>52.277328491210938</v>
+        <v>58.777988433837891</v>
       </c>
     </row>
     <row r="8">
@@ -185,10 +185,10 @@
         <v>2007</v>
       </c>
       <c r="C8" s="1">
-        <v>0.16549938917160034</v>
+        <v>0.1750040203332901</v>
       </c>
       <c r="D8" s="1">
-        <v>16.549938201904297</v>
+        <v>17.500402450561523</v>
       </c>
     </row>
     <row r="9">
@@ -199,10 +199,10 @@
         <v>2007</v>
       </c>
       <c r="C9" s="1">
-        <v>0.47238099575042725</v>
+        <v>0.53207564353942871</v>
       </c>
       <c r="D9" s="1">
-        <v>47.23809814453125</v>
+        <v>53.207565307617188</v>
       </c>
     </row>
     <row r="10">
@@ -213,10 +213,10 @@
         <v>2008</v>
       </c>
       <c r="C10" s="1">
-        <v>0.1466623991727829</v>
+        <v>0.15337283909320831</v>
       </c>
       <c r="D10" s="1">
-        <v>14.666239738464355</v>
+        <v>15.337284088134766</v>
       </c>
     </row>
     <row r="11">
@@ -227,10 +227,10 @@
         <v>2008</v>
       </c>
       <c r="C11" s="1">
-        <v>0.44468063116073608</v>
+        <v>0.50713837146759033</v>
       </c>
       <c r="D11" s="1">
-        <v>44.468063354492188</v>
+        <v>50.713836669921875</v>
       </c>
     </row>
     <row r="12">
@@ -241,10 +241,10 @@
         <v>2009</v>
       </c>
       <c r="C12" s="1">
-        <v>0.16341230273246765</v>
+        <v>0.17369054257869721</v>
       </c>
       <c r="D12" s="1">
-        <v>16.341230392456055</v>
+        <v>17.369054794311523</v>
       </c>
     </row>
     <row r="13">
@@ -255,10 +255,10 @@
         <v>2009</v>
       </c>
       <c r="C13" s="1">
-        <v>0.42219215631484985</v>
+        <v>0.49491226673126221</v>
       </c>
       <c r="D13" s="1">
-        <v>42.219215393066406</v>
+        <v>49.491226196289063</v>
       </c>
     </row>
     <row r="14">
@@ -269,10 +269,10 @@
         <v>2010</v>
       </c>
       <c r="C14" s="1">
-        <v>0.137997105717659</v>
+        <v>0.1505560576915741</v>
       </c>
       <c r="D14" s="1">
-        <v>13.799710273742676</v>
+        <v>15.055605888366699</v>
       </c>
     </row>
     <row r="15">
@@ -283,10 +283,10 @@
         <v>2010</v>
       </c>
       <c r="C15" s="1">
-        <v>0.37584757804870605</v>
+        <v>0.44282487034797669</v>
       </c>
       <c r="D15" s="1">
-        <v>37.584758758544922</v>
+        <v>44.282485961914063</v>
       </c>
     </row>
     <row r="16">
@@ -297,10 +297,10 @@
         <v>2011</v>
       </c>
       <c r="C16" s="1">
-        <v>0.10620803385972977</v>
+        <v>0.1119680255651474</v>
       </c>
       <c r="D16" s="1">
-        <v>10.620803833007813</v>
+        <v>11.196802139282227</v>
       </c>
     </row>
     <row r="17">
@@ -311,10 +311,10 @@
         <v>2011</v>
       </c>
       <c r="C17" s="1">
-        <v>0.35858657956123352</v>
+        <v>0.41748175024986267</v>
       </c>
       <c r="D17" s="1">
-        <v>35.858657836914063</v>
+        <v>41.748176574707031</v>
       </c>
     </row>
     <row r="18">
@@ -325,10 +325,10 @@
         <v>2012</v>
       </c>
       <c r="C18" s="1">
-        <v>0.093334563076496124</v>
+        <v>0.10447204858064651</v>
       </c>
       <c r="D18" s="1">
-        <v>9.3334560394287109</v>
+        <v>10.44720458984375</v>
       </c>
     </row>
     <row r="19">
@@ -339,10 +339,10 @@
         <v>2012</v>
       </c>
       <c r="C19" s="1">
-        <v>0.33575275540351868</v>
+        <v>0.40468284487724304</v>
       </c>
       <c r="D19" s="1">
-        <v>33.575275421142578</v>
+        <v>40.468284606933594</v>
       </c>
     </row>
     <row r="20">
@@ -353,10 +353,10 @@
         <v>2013</v>
       </c>
       <c r="C20" s="1">
-        <v>0.10433327406644821</v>
+        <v>0.10914913564920425</v>
       </c>
       <c r="D20" s="1">
-        <v>10.433327674865723</v>
+        <v>10.914913177490234</v>
       </c>
     </row>
     <row r="21">
@@ -367,10 +367,10 @@
         <v>2013</v>
       </c>
       <c r="C21" s="1">
-        <v>0.27554073929786682</v>
+        <v>0.32772389054298401</v>
       </c>
       <c r="D21" s="1">
-        <v>27.554073333740234</v>
+        <v>32.772388458251953</v>
       </c>
     </row>
     <row r="22">
@@ -381,10 +381,10 @@
         <v>2014</v>
       </c>
       <c r="C22" s="1">
-        <v>0.093987651169300079</v>
+        <v>0.10220518708229065</v>
       </c>
       <c r="D22" s="1">
-        <v>9.3987655639648438</v>
+        <v>10.220519065856934</v>
       </c>
     </row>
     <row r="23">
@@ -395,10 +395,10 @@
         <v>2014</v>
       </c>
       <c r="C23" s="1">
-        <v>0.2329980880022049</v>
+        <v>0.28343620896339417</v>
       </c>
       <c r="D23" s="1">
-        <v>23.299808502197266</v>
+        <v>28.343620300292969</v>
       </c>
     </row>
     <row r="24">
@@ -409,10 +409,10 @@
         <v>2015</v>
       </c>
       <c r="C24" s="1">
-        <v>0.091915257275104523</v>
+        <v>0.10255714505910873</v>
       </c>
       <c r="D24" s="1">
-        <v>9.1915254592895508</v>
+        <v>10.255714416503906</v>
       </c>
     </row>
     <row r="25">
@@ -423,10 +423,10 @@
         <v>2015</v>
       </c>
       <c r="C25" s="1">
-        <v>0.2568906843662262</v>
+        <v>0.32344520092010498</v>
       </c>
       <c r="D25" s="1">
-        <v>25.689067840576172</v>
+        <v>32.344520568847656</v>
       </c>
     </row>
     <row r="26">
@@ -437,10 +437,10 @@
         <v>2016</v>
       </c>
       <c r="C26" s="1">
-        <v>0.095930710434913635</v>
+        <v>0.10758725553750992</v>
       </c>
       <c r="D26" s="1">
-        <v>9.5930709838867188</v>
+        <v>10.758725166320801</v>
       </c>
     </row>
     <row r="27">
@@ -451,10 +451,10 @@
         <v>2016</v>
       </c>
       <c r="C27" s="1">
-        <v>0.25424745678901672</v>
+        <v>0.32600632309913635</v>
       </c>
       <c r="D27" s="1">
-        <v>25.424745559692383</v>
+        <v>32.600631713867188</v>
       </c>
     </row>
     <row r="28">
@@ -465,10 +465,10 @@
         <v>2017</v>
       </c>
       <c r="C28" s="1">
-        <v>0.075294040143489838</v>
+        <v>0.085557818412780762</v>
       </c>
       <c r="D28" s="1">
-        <v>7.5294041633605957</v>
+        <v>8.5557823181152344</v>
       </c>
     </row>
     <row r="29">
@@ -479,10 +479,10 @@
         <v>2017</v>
       </c>
       <c r="C29" s="1">
-        <v>0.26572322845458984</v>
+        <v>0.33692410588264465</v>
       </c>
       <c r="D29" s="1">
-        <v>26.572322845458984</v>
+        <v>33.692409515380859</v>
       </c>
     </row>
     <row r="30">
@@ -493,10 +493,10 @@
         <v>2018</v>
       </c>
       <c r="C30" s="1">
-        <v>0.091392524540424347</v>
+        <v>0.15381067991256714</v>
       </c>
       <c r="D30" s="1">
-        <v>9.1392526626586914</v>
+        <v>15.381068229675293</v>
       </c>
     </row>
     <row r="31">
@@ -507,10 +507,10 @@
         <v>2018</v>
       </c>
       <c r="C31" s="1">
-        <v>0.25740653276443482</v>
+        <v>0.40019217133522034</v>
       </c>
       <c r="D31" s="1">
-        <v>25.740653991699219</v>
+        <v>40.019218444824219</v>
       </c>
     </row>
     <row r="32">
@@ -521,10 +521,10 @@
         <v>2019</v>
       </c>
       <c r="C32" s="1">
-        <v>0.10099571198225021</v>
+        <v>0.11260735988616943</v>
       </c>
       <c r="D32" s="1">
-        <v>10.099571228027344</v>
+        <v>11.260736465454102</v>
       </c>
     </row>
     <row r="33">
@@ -535,10 +535,10 @@
         <v>2019</v>
       </c>
       <c r="C33" s="1">
-        <v>0.27531349658966064</v>
+        <v>0.36291363835334778</v>
       </c>
       <c r="D33" s="1">
-        <v>27.531349182128906</v>
+        <v>36.291362762451172</v>
       </c>
     </row>
     <row r="34">
@@ -549,10 +549,10 @@
         <v>2020</v>
       </c>
       <c r="C34" s="1">
-        <v>0.16245433688163757</v>
+        <v>0.17895083129405975</v>
       </c>
       <c r="D34" s="1">
-        <v>16.245433807373047</v>
+        <v>17.895082473754883</v>
       </c>
     </row>
     <row r="35">
@@ -563,10 +563,10 @@
         <v>2020</v>
       </c>
       <c r="C35" s="1">
-        <v>0.32439887523651123</v>
+        <v>0.41978952288627625</v>
       </c>
       <c r="D35" s="1">
-        <v>32.439888000488281</v>
+        <v>41.978950500488281</v>
       </c>
     </row>
     <row r="36">
@@ -577,10 +577,10 @@
         <v>2021</v>
       </c>
       <c r="C36" s="1">
-        <v>0.13367976248264313</v>
+        <v>0.1448843777179718</v>
       </c>
       <c r="D36" s="1">
-        <v>13.367976188659668</v>
+        <v>14.488437652587891</v>
       </c>
     </row>
     <row r="37">
@@ -591,10 +591,10 @@
         <v>2021</v>
       </c>
       <c r="C37" s="1">
-        <v>0.31801047921180725</v>
+        <v>0.37165451049804688</v>
       </c>
       <c r="D37" s="1">
-        <v>31.801048278808594</v>
+        <v>37.165451049804688</v>
       </c>
     </row>
     <row r="38">
@@ -605,10 +605,10 @@
         <v>2022</v>
       </c>
       <c r="C38" s="1">
-        <v>0.10246961563825607</v>
+        <v>0.11114632338285446</v>
       </c>
       <c r="D38" s="1">
-        <v>10.24696159362793</v>
+        <v>11.114632606506348</v>
       </c>
     </row>
     <row r="39">
@@ -619,10 +619,10 @@
         <v>2022</v>
       </c>
       <c r="C39" s="1">
-        <v>0.29510417580604553</v>
+        <v>0.35011890530586243</v>
       </c>
       <c r="D39" s="1">
-        <v>29.510417938232422</v>
+        <v>35.011890411376953</v>
       </c>
     </row>
     <row r="40">
@@ -633,10 +633,10 @@
         <v>2023</v>
       </c>
       <c r="C40" s="1">
-        <v>0.10493046045303345</v>
+        <v>0.11362532526254654</v>
       </c>
       <c r="D40" s="1">
-        <v>10.493045806884766</v>
+        <v>11.362532615661621</v>
       </c>
     </row>
     <row r="41">
@@ -647,10 +647,10 @@
         <v>2023</v>
       </c>
       <c r="C41" s="1">
-        <v>0.29806560277938843</v>
+        <v>0.35193449258804321</v>
       </c>
       <c r="D41" s="1">
-        <v>29.806560516357422</v>
+        <v>35.193450927734375</v>
       </c>
     </row>
     <row r="42">
@@ -661,10 +661,10 @@
         <v>2024</v>
       </c>
       <c r="C42" s="1">
-        <v>0.10534298419952393</v>
+        <v>0.12021598964929581</v>
       </c>
       <c r="D42" s="1">
-        <v>10.534297943115234</v>
+        <v>12.021598815917969</v>
       </c>
     </row>
     <row r="43">
@@ -675,10 +675,10 @@
         <v>2024</v>
       </c>
       <c r="C43" s="1">
-        <v>0.31973597407341004</v>
+        <v>0.36946329474449158</v>
       </c>
       <c r="D43" s="1">
-        <v>31.973596572875977</v>
+        <v>36.946331024169922</v>
       </c>
     </row>
     <row r="44">
@@ -689,10 +689,10 @@
         <v>2025</v>
       </c>
       <c r="C44" s="1">
-        <v>0.090681187808513641</v>
+        <v>0.095277689397335053</v>
       </c>
       <c r="D44" s="1">
-        <v>9.0681190490722656</v>
+        <v>9.5277690887451172</v>
       </c>
     </row>
     <row r="45">
@@ -703,10 +703,10 @@
         <v>2025</v>
       </c>
       <c r="C45" s="1">
-        <v>0.26905199885368347</v>
+        <v>0.30702796578407288</v>
       </c>
       <c r="D45" s="1">
-        <v>26.90519905090332</v>
+        <v>30.702796936035156</v>
       </c>
     </row>
   </sheetData>
